--- a/xls/fx.xlsx
+++ b/xls/fx.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>id</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>"angle":{"from":-15,"to":15},"duration":400,"yoyo":true,"repeat":-1,"ease":"Sine.InOut"</t>
+  </si>
+  <si>
+    <t>"scale":{"from":1,"to":1.4},"duration":150,"yoyo":true,"ease":"Quad.Out"</t>
   </si>
 </sst>
 </file>
@@ -451,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.57" customWidth="1"/>
@@ -485,7 +488,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="31.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -508,7 +511,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" ht="31.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -518,15 +521,21 @@
       <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/xls/fx.xlsx
+++ b/xls/fx.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -34,6 +34,9 @@
     <t>end</t>
   </si>
   <si>
+    <t>body</t>
+  </si>
+  <si>
     <t>burn</t>
   </si>
   <si>
@@ -64,10 +67,10 @@
     <t>"size":20,"align":"top"</t>
   </si>
   <si>
-    <t>"angle":{"from":-15,"to":15},"duration":400,"yoyo":true,"repeat":-1,"ease":"Sine.InOut"</t>
-  </si>
-  <si>
     <t>"scale":{"from":1,"to":1.4},"duration":150,"yoyo":true,"ease":"Quad.Out"</t>
+  </si>
+  <si>
+    <t>"angle":{"from":-8,"to":8},"duration":400,"yoyo":true,"repeat":-1,"ease":"Sine.InOut"</t>
   </si>
 </sst>
 </file>
@@ -462,10 +465,10 @@
     <col min="3" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="50" customWidth="1"/>
-    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="7" max="8" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,52 +489,57 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="H2" s="1"/>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/xls/fx.xlsx
+++ b/xls/fx.xlsx
@@ -70,7 +70,7 @@
     <t>"scale":{"from":1,"to":1.4},"duration":150,"yoyo":true,"ease":"Quad.Out"</t>
   </si>
   <si>
-    <t>"angle":{"from":-8,"to":8},"duration":400,"yoyo":true,"repeat":-1,"ease":"Sine.InOut"</t>
+    <t>"angle":{"from":-2.5,"to":2.5},"duration":500,"yoyo":true,"repeat":-1,"ease":"Sine.InOut"</t>
   </si>
 </sst>
 </file>

--- a/xls/fx.xlsx
+++ b/xls/fx.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>id</t>
   </si>
@@ -43,7 +43,7 @@
     <t>🔥</t>
   </si>
   <si>
-    <t>"size":20,"alpha":0.8,"align":"bottom","oy":0</t>
+    <t>"size":20,"alpha":0.8,"align":"bottom","oy":0,"flash":true</t>
   </si>
   <si>
     <t>"scale":{"from":0,"to":1},"duration":200,"ease":"Back.Out"</t>
@@ -71,6 +71,21 @@
   </si>
   <si>
     <t>"angle":{"from":-2.5,"to":2.5},"duration":500,"yoyo":true,"repeat":-1,"ease":"Sine.InOut"</t>
+  </si>
+  <si>
+    <t>poison</t>
+  </si>
+  <si>
+    <t>☠️</t>
+  </si>
+  <si>
+    <t>"size":20,"align":"bottom","flash":true</t>
+  </si>
+  <si>
+    <t>"scale":{"from":0.3,"to":1},"alpha":{"from":0,"to":1},"y":"-=24","duration":500,"ease":"Sine.Out"</t>
+  </si>
+  <si>
+    <t>"y":"-=8","alpha":0,"duration":300,"ease":"Quad.In"</t>
   </si>
 </sst>
 </file>
@@ -457,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.57" customWidth="1"/>
@@ -542,6 +557,26 @@
         <v>19</v>
       </c>
     </row>
+    <row r="4" ht="31.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/xls/fx.xlsx
+++ b/xls/fx.xlsx
@@ -79,7 +79,7 @@
     <t>☠️</t>
   </si>
   <si>
-    <t>"size":20,"align":"bottom","flash":true</t>
+    <t>"size":20,"align":"center","flash":true</t>
   </si>
   <si>
     <t>"scale":{"from":0.3,"to":1},"alpha":{"from":0,"to":1},"y":"-=24","duration":500,"ease":"Sine.Out"</t>
